--- a/Fase 1/Evidencias Grupales/Plantilla_Registro_Uso_IA_Capstone.xlsx
+++ b/Fase 1/Evidencias Grupales/Plantilla_Registro_Uso_IA_Capstone.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jorge\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42577721-764D-41D4-AF9C-8C62F9369E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Registro IA" sheetId="1" r:id="rId4"/>
+    <sheet name="Registro IA" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="Z_EC5239EE_3F4D_4BBD_BF52_AC40B64EB91E_.wvu.FilterData">'Registro IA'!$A$1:$L$21</definedName>
+    <definedName name="Z_AD2ED932_5B4F_4F90_9477_F15741C64DFD_.wvu.FilterData" localSheetId="0" hidden="1">'Registro IA'!$A$1:$L$35</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{EC5239EE-3F4D-4BBD-BF52-AC40B64EB91E}" name="RegistroIA filter view"/>
+    <customWorkbookView name="RegistroIA filter view" guid="{AD2ED932-5B4F-4F90-9477-F15741C64DFD}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ypnp3mAsYqnCNVT9JyW4B/W68Wdq8B0zlz4nf0D1ziQ="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="189">
   <si>
     <t>Fase</t>
   </si>
@@ -59,51 +64,1348 @@
     <t>Observaciones</t>
   </si>
   <si>
-    <t>Rodrigo Lopez</t>
+    <t>Definición del proyecto</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>Luz Hermosilla</t>
   </si>
   <si>
     <t>ChatGPT</t>
   </si>
   <si>
-    <t>Sol5.6</t>
-  </si>
-  <si>
-    <t>Generacion e implementacion de ambiente de prueba en arquitectura Azure, generacion de diagramas de arquitectura</t>
-  </si>
-  <si>
-    <t>Conversacion de aproximadamente 30 mensajes donde se entrega contexto del caso y se sigue paso a paso el proceso de implementacion</t>
-  </si>
-  <si>
-    <t>Plataforma en construccion para simular arquitectura Azure multitenant, diagramas de arquitectura e informe</t>
-  </si>
-  <si>
-    <t>Se verifico empiricamente el procedimiento a travez de la plataforma Azure</t>
+    <t>No documentado</t>
+  </si>
+  <si>
+    <t>Analiza los documentos del proyecto SSO y ayúdame a identificar funcionalidades y requerimientos.</t>
+  </si>
+  <si>
+    <t>Planificación Scrum</t>
+  </si>
+  <si>
+    <t>02/09/2026</t>
+  </si>
+  <si>
+    <t>Ayúdame a construir las historias de usuario y el User Story Mapping del proyecto SSO.</t>
+  </si>
+  <si>
+    <t>Documentación APT</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>Trabajemos el informe APT por apartados conforme a la guía de evaluación.</t>
+  </si>
+  <si>
+    <t>Gestión Jira</t>
+  </si>
+  <si>
+    <t>24/09/2026</t>
+  </si>
+  <si>
+    <t>Explícame cómo exportar Jira y ordenar épicas, historias y subtareas con responsables.</t>
+  </si>
+  <si>
+    <t>Monitoreo Scrum</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>Ayúdame a identificar épicas, historias, subtareas y sus estados en Jira.</t>
+  </si>
+  <si>
+    <t>Seguimiento de avance</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
+    <t>Revisa el resumen de avance del proyecto según los estados de Jira.</t>
+  </si>
+  <si>
+    <t>Ajustes al plan</t>
+  </si>
+  <si>
+    <t>Revisa los ajustes a partir del monitoreo y el plan de trabajo.</t>
+  </si>
+  <si>
+    <t>Planificación de releases</t>
+  </si>
+  <si>
+    <t>Adapta el Release Plan al formato del profesor, con seis sprints y cierre el 13 de noviembre.</t>
+  </si>
+  <si>
+    <t>Definición tecnológica</t>
+  </si>
+  <si>
+    <t>Revisa la lámina de tecnologías del módulo y sustituye OCR por LangChain.</t>
+  </si>
+  <si>
+    <t>Presentación Capstone</t>
+  </si>
+  <si>
+    <t>Revisa descripción, objetivos, alcance, limitaciones y metodología de la presentación.</t>
+  </si>
+  <si>
+    <t>Apoyo para comprender y sintetizar documentación entregada sobre el sistema SSO.</t>
+  </si>
+  <si>
+    <t>Síntesis preliminar de funcionalidades y requerimientos para revisión.</t>
+  </si>
+  <si>
+    <t>Se seleccionó y reformuló contenido para el contexto del proyecto.</t>
+  </si>
+  <si>
+    <t>Contrastado durante la revisión con documentos aportados; no constituye validación técnica.</t>
+  </si>
+  <si>
+    <t>Agilizó la lectura y organización de antecedentes.</t>
+  </si>
+  <si>
+    <t>La interpretación y selección de contenidos correspondió al equipo.</t>
+  </si>
+  <si>
+    <t>Apoyo para redactar y organizar historias de usuario y User Story Mapping.</t>
+  </si>
+  <si>
+    <t>Borradores de historias de usuario y propuesta de agrupación funcional.</t>
+  </si>
+  <si>
+    <t>Se ajustó la redacción y organización a los requerimientos compartidos.</t>
+  </si>
+  <si>
+    <t>Se revisó la correspondencia con documentación y estructura de Jira; validar aceptación final en el equipo.</t>
+  </si>
+  <si>
+    <t>Facilitó la preparación de borradores y su revisión.</t>
+  </si>
+  <si>
+    <t>No atribuye a IA la aprobación de historias ni la gestión directa de Jira.</t>
+  </si>
+  <si>
+    <t>Apoyo editorial para adaptar textos a la guía APT.</t>
+  </si>
+  <si>
+    <t>Borradores de secciones del informe académico.</t>
+  </si>
+  <si>
+    <t>Se acortaron y adaptaron textos según los apartados solicitados.</t>
+  </si>
+  <si>
+    <t>Comparación del texto con la guía y la documentación entregada.</t>
+  </si>
+  <si>
+    <t>Redujo el tiempo de preparación de borradores.</t>
+  </si>
+  <si>
+    <t>La revisión y entrega académica son responsabilidad de los estudiantes.</t>
+  </si>
+  <si>
+    <t>Orientación para consultar Jira y ordenar información exportada.</t>
+  </si>
+  <si>
+    <t>Instrucciones de consulta y propuesta de organización EP–HU–ST.</t>
+  </si>
+  <si>
+    <t>Se corrigieron asociaciones y responsables según las capturas facilitadas.</t>
+  </si>
+  <si>
+    <t>Se contrastaron las propuestas con las vistas y archivos de Jira compartidos.</t>
+  </si>
+  <si>
+    <t>Facilitó el ordenamiento y seguimiento de información.</t>
+  </si>
+  <si>
+    <t>No se utilizó IA para ejecutar cambios directamente en Jira.</t>
+  </si>
+  <si>
+    <t>Orientación para interpretar estados y relaciones entre tareas en Jira.</t>
+  </si>
+  <si>
+    <t>Explicaciones paso a paso para consultar tareas, estados y vínculos.</t>
+  </si>
+  <si>
+    <t>Se ajustaron las explicaciones a las pantallas disponibles en Jira.</t>
+  </si>
+  <si>
+    <t>Se compararon con capturas del tablero y backlog aportadas.</t>
+  </si>
+  <si>
+    <t>Ayudó a comprender la navegación y el seguimiento.</t>
+  </si>
+  <si>
+    <t>La información oficial se mantiene en Jira.</t>
+  </si>
+  <si>
+    <t>Apoyo de redacción del resumen de avance a partir de datos proporcionados.</t>
+  </si>
+  <si>
+    <t>Borrador de resumen con estados y pendientes reportados.</t>
+  </si>
+  <si>
+    <t>Se ajustó la redacción para diferenciar trabajo terminado y pendiente.</t>
+  </si>
+  <si>
+    <t>Las cifras se cotejaron con el corte de Jira compartido; requieren actualización antes de entrega.</t>
+  </si>
+  <si>
+    <t>Facilitó la elaboración del informe de avance.</t>
+  </si>
+  <si>
+    <t>Los datos son de un corte específico, no evidencia de cierre definitivo.</t>
+  </si>
+  <si>
+    <t>Apoyo editorial para explicar ajustes al plan y al backlog.</t>
+  </si>
+  <si>
+    <t>Borrador de texto sobre cambios de alcance y actividades paralelas.</t>
+  </si>
+  <si>
+    <t>Se corrigió el texto para reflejar ocho épicas y seis sprints.</t>
+  </si>
+  <si>
+    <t>Se revisó coherencia con el plan de trabajo y registros de Jira disponibles.</t>
+  </si>
+  <si>
+    <t>Mejoró la claridad del apartado de monitoreo.</t>
+  </si>
+  <si>
+    <t>La aprobación de cambios del proyecto corresponde al equipo.</t>
+  </si>
+  <si>
+    <t>Apoyo para diagramar el Release Plan según plantilla docente.</t>
+  </si>
+  <si>
+    <t>Borradores gráficos y propuestas de hitos y cronograma.</t>
+  </si>
+  <si>
+    <t>Se solicitaron correcciones de fechas, formato y ubicación de reportes antes de LangChain.</t>
+  </si>
+  <si>
+    <t>Se contrastaron borradores con el formato del profesor y fechas proporcionadas; versión final sujeta a revisión.</t>
+  </si>
+  <si>
+    <t>Aportó propuestas visuales, con varias iteraciones necesarias.</t>
+  </si>
+  <si>
+    <t>No presentar borradores de IA como cronograma aprobado ni fechas inferidas como reales.</t>
+  </si>
+  <si>
+    <t>Apoyo editorial para actualizar la lámina de tecnologías.</t>
+  </si>
+  <si>
+    <t>Propuesta de redacción que destaca LangChain y elimina OCR como tecnología prevista en esta etapa.</t>
+  </si>
+  <si>
+    <t>Se pidió adecuar el contenido a la decisión comunicada por el equipo.</t>
+  </si>
+  <si>
+    <t>Coherencia revisada con las indicaciones del equipo; implementación técnica no verificada por IA.</t>
+  </si>
+  <si>
+    <t>Ayudó a mantener consistencia terminológica.</t>
+  </si>
+  <si>
+    <t>La selección e implementación tecnológica corresponde al equipo de desarrollo.</t>
+  </si>
+  <si>
+    <t>Apoyo en la revisión de redacción y coherencia entre diapositivas.</t>
+  </si>
+  <si>
+    <t>Observaciones y propuestas de texto para descripción, objetivos, alcance y Scrum.</t>
+  </si>
+  <si>
+    <t>Se aceptaron, rechazaron o corrigieron sugerencias según el material revisado.</t>
+  </si>
+  <si>
+    <t>Comparación con las diapositivas y acuerdos aportados; aprobación final del equipo pendiente.</t>
+  </si>
+  <si>
+    <t>Facilitó la revisión editorial de la presentación.</t>
+  </si>
+  <si>
+    <t>No implica que IA haya diseñado, desarrollado o probado el sistema.</t>
+  </si>
+  <si>
+    <t>Diseño y Arquitectura</t>
+  </si>
+  <si>
+    <t>Cristóbal González</t>
+  </si>
+  <si>
+    <t>Google Gemini / LangChain</t>
+  </si>
+  <si>
+    <t>Gemini 1.5 Flash</t>
+  </si>
+  <si>
+    <t>Diseñar la arquitectura del endpoint de previsualización OCR para la toma de asistencia en Diálogos de Seguridad (ST-35).</t>
+  </si>
+  <si>
+    <t>Diseñar el esquema de datos y el flujo de trabajo en FastAPI para recibir una imagen de asistencia y retornar un JSON con trabajadores detectados y su nivel de coincidencia usando LangChain y Gemini.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Definición de contrato API para </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>/api/v1/attendance/ocr/preview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>, estructuras Pydantic y estrategia de matching de trabajadores.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se adaptó el esquema para incluir campos </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>client_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>talk_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y filtrado estricto por la base de datos MongoDB del cliente.</t>
+    </r>
+  </si>
+  <si>
+    <t>Revisión de arquitectura y pruebas de contrato de interfaz en OpenAPI/Swagger.</t>
+  </si>
+  <si>
+    <t>Reducción de 6 horas en diseño de arquitectura a 1 hora.</t>
+  </si>
+  <si>
+    <t>Integración exitosa con arquitectura de microservicios FastAPI.</t>
+  </si>
+  <si>
+    <t>Desarrollo Backend</t>
+  </si>
+  <si>
+    <t>Google Gemini</t>
+  </si>
+  <si>
+    <t>Gemini 1.5 Pro</t>
+  </si>
+  <si>
+    <r>
+      <t>Implementar el pipeline de reconocimiento OCR y la lógica de correspondencia (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>matching</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) de trabajadores en </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>talks-service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Crear función en Python para procesar el texto detectado por Gemini OCR y emparejarlo con la lista de usuarios activos de la empresa en MongoDB, asignando estados suggested, ambiguous o unmatched.</t>
+  </si>
+  <si>
+    <t>Código Python con la lógica del pipeline de procesamiento de imágenes y algoritmo de similitud para nombres.</t>
+  </si>
+  <si>
+    <r>
+      <t>Ajuste en los umbrales de coincidencia (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>score &gt;= 0.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) y tratamiento de nombres y apellidos según formato chileno.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ejecución de casos de prueba unitarios con listas de asistencia escaneadas simuladas.</t>
+  </si>
+  <si>
+    <t>Ahorro de ~8 horas de desarrollo manual de algoritmos de parsing.</t>
+  </si>
+  <si>
+    <t>Permite procesar hojas manuscritas y digitales con alto nivel de precisión.</t>
+  </si>
+  <si>
+    <t>Pruebas y QA</t>
+  </si>
+  <si>
+    <t>Asistente IA</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Resolver fallos de configuración de variables de entorno y fallos de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>pytest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> en el entorno de pruebas de integración de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>talks-service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Resolver RuntimeError: MONGO_DB debe ser exactamente sso_riesgo_qr_test y errores de validación de QR_SIGNING_SECRET de menos de 32 caracteres al ejecutar pytest.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Refactorización de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>tests/conftest.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> para forzar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>override=True</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>.env.test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> e inyectar claves de 32+ caracteres automáticamente.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se incorporó la carga explícita de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>dotenv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> antes de importar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>app.dep_talks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y generación dinámica de secrets con </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>secrets.token_hex(32)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ejecución limpia de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>python -m pytest tests/integration/test_ocr_attendance.py -v</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> en PowerShell sin errores de entorno.</t>
+    </r>
+  </si>
+  <si>
+    <t>Resolución de bloqueo técnico en pruebas en menos de 30 minutos.</t>
+  </si>
+  <si>
+    <t>Garantizó la seguridad del entorno de pruebas aislando la base de datos.</t>
+  </si>
+  <si>
+    <t>Desarrollo Frontend</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Crear el componente React </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>ParticipantScanner.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y el hook </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>useParticipantScan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> para la interfaz de usuario.</t>
+    </r>
+  </si>
+  <si>
+    <t>Crear un componente en React + TypeScript (ParticipantScanner) que consuma /api/v1/attendance/ocr/preview, muestre la vista previa de la imagen, barra de progreso y la tabla con estatus de coincidencia.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Componentes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>ParticipantScanner.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y hook </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>useParticipantScan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> con manejo de estados </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>idle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>processing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>results</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>error</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Se unificó la lógica del escáner con Lucide React icons y se estructuró la confirmación individual o masiva de asistentes.</t>
+  </si>
+  <si>
+    <t>Prueba de renderizado e integración visual en el navegador web.</t>
+  </si>
+  <si>
+    <t>Desarrollo de UI fluida y responsive en 2 horas.</t>
+  </si>
+  <si>
+    <t>Excelente experiencia de usuario con badges de estatus de coincidencia.</t>
+  </si>
+  <si>
+    <t>Integración de Sistemas</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Integrar el componente de escaneo OCR dentro del panel lateral de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>SafetyTalks.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y registrar la navegación en </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>App.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Integrar el botón Escaneo LangChain en SafetyTalks.tsx para abrir ParticipantScanner y agregar el módulo ST-35 en allModules dentro de App.tsx.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Código integrado de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>SafetyTalks.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> con flujo de confirmación directa a la API de asistencias y actualización de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>App.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se vinculó el envío de la lista confirmada directamente al endpoint </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>POST /v1/attendance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> para persistencia en MongoDB.</t>
+    </r>
+  </si>
+  <si>
+    <t>Prueba de flujo end-to-end desde la subida de imagen hasta la actualización de la lista de asistentes en pantalla.</t>
+  </si>
+  <si>
+    <t>Completación integral del requerimiento ST-35.</t>
+  </si>
+  <si>
+    <t>Integración limpia sin romper los módulos existentes de Vigía Industrial.</t>
+  </si>
+  <si>
+    <t>Integración IA</t>
+  </si>
+  <si>
+    <t>Jorge Solis</t>
+  </si>
+  <si>
+    <t>Apoyo para definir la integración de LangChain y Gemini en el procesamiento de asistencia mediante imágenes.</t>
+  </si>
+  <si>
+    <t>Ayúdame a integrar LangChain y Gemini al flujo existente para extraer asistentes desde una imagen, permitir su revisión y confirmación antes de guardar.</t>
+  </si>
+  <si>
+    <t>Propuesta de flujo de previsualización, extracción de nombres/correos, asociación con usuarios registrados y confirmación humana.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se ajustó el diseño para que Gemini sea consumido desde </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>talks-service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, mantener la imagen separada del registro definitivo y utilizar identificadores de usuario y tenant.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se contrastó la propuesta con el flujo existente de asistencia, aislamiento por </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>client_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> y requerimiento de revisión antes de persistir información.</t>
+    </r>
+  </si>
+  <si>
+    <t>Permitió definir la integración antes de modificar el flujo existente y reducir posibles errores de diseño.</t>
+  </si>
+  <si>
+    <t>La configuración técnica y la implementación definitiva deben ser validadas mediante pruebas del sistema.</t>
+  </si>
+  <si>
+    <t>Integración de código</t>
+  </si>
+  <si>
+    <t>Apoyo para integrar de forma controlada los cambios de LangChain y Gemini desarrollados por otro integrante.</t>
+  </si>
+  <si>
+    <t>Revisa los cambios de la rama de LangChain y ayúdame a integrar solamente los archivos que supervisé, excluyendo los tests que no corresponden.</t>
+  </si>
+  <si>
+    <t>Estrategia de integración selectiva mediante Git para conservar únicamente los archivos relacionados con la implementación supervisada.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se identificaron cuatro archivos del módulo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>talks-service/app/ai/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> como parte del cambio válido y se excluyeron dos pruebas que no habían sido supervisadas.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se revisaron commits, archivos modificados y diferencias antes de preparar la integración hacia </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Redujo el riesgo de incorporar código no revisado y mejoró la trazabilidad de la integración.</t>
+  </si>
+  <si>
+    <t>La decisión final sobre qué código integrar correspondió al responsable de la revisión.</t>
+  </si>
+  <si>
+    <t>Configuración técnica SSO</t>
+  </si>
+  <si>
+    <t>Apoyo para analizar la migración de persistencia y verificar el funcionamiento de los microservicios del sistema SSO.</t>
+  </si>
+  <si>
+    <t>Ayúdame a revisar los microservicios actuales y a definir cómo migrar la persistencia hacia MongoDB sin romper los contratos existentes.</t>
+  </si>
+  <si>
+    <t>Propuesta de mantener routers, schemas y contratos, modificando principalmente la capa de persistencia y validando cada servicio individualmente.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se revisó la estrategia de conexión a MongoDB y la necesidad de mantener aislamiento mediante </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>client_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, JWT y contratos existentes.</t>
+    </r>
+  </si>
+  <si>
+    <t>Se comprobó posteriormente que los nueve microservicios respondían en sus respectivos puertos y podían continuar utilizándose como base del proyecto.</t>
+  </si>
+  <si>
+    <t>Facilitó el diagnóstico de la arquitectura existente y evitó cambios innecesarios en servicios funcionales.</t>
+  </si>
+  <si>
+    <t>La IA apoyó el análisis técnico; la ejecución y comprobación de los servicios se realizó en el entorno del proyecto.</t>
+  </si>
+  <si>
+    <t>Integración Web SSO</t>
+  </si>
+  <si>
+    <t>Apoyo para diagnosticar problemas de red y comunicación entre WebSSO, Nginx y los servicios Docker.</t>
+  </si>
+  <si>
+    <t>Revisa por qué WebSSO no logra comunicarse correctamente con los servicios y ayúdame a validar la configuración de Docker y Nginx.</t>
+  </si>
+  <si>
+    <t>Diagnóstico de redes Docker separadas y propuesta de conectar el contenedor web con la red utilizada por los servicios SSO.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se ajustó la conexión de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>sso-web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> a la red correspondiente y se revisó el proxy de autenticación.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se verificó que </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/api/auth/v1/auth/me</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> respondiera desde WebSSO; el </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>401</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sin JWT confirmó que la ruta y el proxy estaban alcanzando Auth Service.</t>
+    </r>
+  </si>
+  <si>
+    <t>Redujo el tiempo de diagnóstico y permitió separar problemas de conectividad de problemas propios de autenticación.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">La respuesta </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>401</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fue considerada esperada sin una sesión válida; posteriormente el login requirió revisión adicional.</t>
+    </r>
+  </si>
+  <si>
+    <t>Despliegue y CI/CD</t>
+  </si>
+  <si>
+    <t>GPT-5.6 Sol</t>
+  </si>
+  <si>
+    <t>Apoyo para definir una estrategia de despliegue colaborativo del Dashboard Web en Vercel.</t>
+  </si>
+  <si>
+    <t>Ahora que el proyecto está desplegado mediante Vercel CLI, ¿cómo podemos permitir que los cambios de otros integrantes se desplieguen de forma controlada?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Propuesta de flujo GitHub Actions → Vercel con Preview para Pull Requests y despliegue de producción después de integrar cambios en </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>main</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Se definieron los secretos necesarios, el proyecto de Vercel objetivo y el uso de </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>WebSSO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> como fuente oficial para futuros despliegues.</t>
+    </r>
+  </si>
+  <si>
+    <t>Se comprobó la existencia del proyecto y deployment actual en Vercel; el workflow automatizado todavía no ha sido implementado.</t>
+  </si>
+  <si>
+    <t>Permitirá reducir despliegues manuales y la dependencia de una sola persona para publicar cambios.</t>
+  </si>
+  <si>
+    <t>Corresponde a una propuesta de automatización pendiente de implementación y prueba.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="9">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,69 +1413,65 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{39BB9C30-1313-4E88-B2E0-40998D61F374}"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
-      <font/>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDBE5F1"/>
+          <bgColor rgb="FFDBE5F1"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="4"/>
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB8CCE4"/>
-          <bgColor rgb="FFB8CCE4"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFDBE5F1"/>
-          <bgColor rgb="FFDBE5F1"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
     <dxf>
       <border>
@@ -199,42 +1497,46 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Registro IA-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Registro IA-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:L21" displayName="RegistroIA" name="RegistroIA" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RegistroIA" displayName="RegistroIA" ref="A1:L35">
   <tableColumns count="12">
-    <tableColumn name="Fase" id="1"/>
-    <tableColumn name="Fecha" id="2"/>
-    <tableColumn name="Integrante" id="3"/>
-    <tableColumn name="Herramienta IA" id="4"/>
-    <tableColumn name="Modelo" id="5"/>
-    <tableColumn name="Objetivo del Uso" id="6"/>
-    <tableColumn name="Prompt Utilizado" id="7"/>
-    <tableColumn name="Resultado Generado (Resumen)" id="8"/>
-    <tableColumn name="Modificaciones Realizadas" id="9"/>
-    <tableColumn name="Validación (Cómo se verificó)" id="10"/>
-    <tableColumn name="Impacto (Tiempo/Calidad)" id="11"/>
-    <tableColumn name="Observaciones" id="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Fase"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Fecha"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Integrante"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Herramienta IA"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Modelo"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Objetivo del Uso"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Prompt Utilizado"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Resultado Generado (Resumen)"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Modificaciones Realizadas"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Validación (Cómo se verificó)"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Impacto (Tiempo/Calidad)"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Observaciones"/>
   </tableColumns>
-  <tableStyleInfo name="Registro IA-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Registro IA-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -424,31 +1726,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L999"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.36328125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.43"/>
-    <col customWidth="1" min="2" max="2" width="15.14"/>
-    <col customWidth="1" min="3" max="3" width="23.71"/>
-    <col customWidth="1" min="4" max="5" width="32.29"/>
-    <col customWidth="1" min="6" max="6" width="27.43"/>
-    <col customWidth="1" min="7" max="7" width="45.0"/>
-    <col customWidth="1" min="8" max="8" width="36.14"/>
-    <col customWidth="1" min="9" max="9" width="36.86"/>
-    <col customWidth="1" min="10" max="10" width="37.0"/>
-    <col customWidth="1" min="11" max="11" width="36.43"/>
-    <col customWidth="1" min="12" max="12" width="43.86"/>
-    <col customWidth="1" min="13" max="23" width="8.86"/>
+    <col min="1" max="1" width="17.36328125" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" customWidth="1"/>
+    <col min="4" max="5" width="32.26953125" customWidth="1"/>
+    <col min="6" max="6" width="27.36328125" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="8" max="8" width="36.08984375" customWidth="1"/>
+    <col min="9" max="9" width="36.81640625" customWidth="1"/>
+    <col min="10" max="10" width="37" customWidth="1"/>
+    <col min="11" max="11" width="36.36328125" customWidth="1"/>
+    <col min="12" max="12" width="43.81640625" customWidth="1"/>
+    <col min="13" max="23" width="8.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" ht="14.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,63 +1788,975 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>46268.0</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="2" spans="1:12" ht="58">
+      <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="43.5">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="4" spans="1:12" ht="29">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="43.5">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="43.5">
+      <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="43.5">
+      <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="29">
+      <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="43.5">
+      <c r="A9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="43.5">
+      <c r="A10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="43.5">
+      <c r="A11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="72.5">
+      <c r="A12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46305</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="72.5">
+      <c r="A13" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46307</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="71.5">
+      <c r="A14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46309</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="72.5">
+      <c r="A15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46310</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="71.5">
+      <c r="A16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46311</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="72.5">
+      <c r="A17" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46310</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="72.5">
+      <c r="A18" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46311</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="72.5">
+      <c r="A19" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46291</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="58">
+      <c r="A20" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46309</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="58">
+      <c r="A21" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46311</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+    </row>
+    <row r="24" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+    </row>
+    <row r="26" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+    </row>
+    <row r="27" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+    </row>
+    <row r="28" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+    </row>
+    <row r="29" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+    </row>
+    <row r="30" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+    </row>
+    <row r="31" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+    </row>
+    <row r="33" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+    </row>
+    <row r="34" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+    </row>
+    <row r="35" spans="1:12" ht="15.75" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+    </row>
+    <row r="36" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="37" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="38" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="39" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="40" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="41" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="42" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="43" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="44" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="45" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="46" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="47" spans="1:12" ht="15.75" customHeight="1"/>
+    <row r="48" spans="1:12" ht="15.75" customHeight="1"/>
     <row r="49" ht="15.75" customHeight="1"/>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
@@ -1494,11 +3708,11 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{EC5239EE-3F4D-4BBD-BF52-AC40B64EB91E}" filter="1" showAutoFilter="1">
-      <autoFilter ref="$A$1:$L$21"/>
+    <customSheetView guid="{AD2ED932-5B4F-4F90-9477-F15741C64DFD}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="A1:L21" xr:uid="{48B2F61D-B4EF-47C3-89B3-0D771D0A41B6}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1049182733"/>
@@ -1506,12 +3720,10 @@
       </extLst>
     </customSheetView>
   </customSheetViews>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>